--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260602.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260602.xlsx
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
